--- a/issue_register.xlsx
+++ b/issue_register.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:AF4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,85 +456,135 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Дата начала рейса</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Дата окончания рейса</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Начальник рейса</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>№ этапа рейса</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>№ диска</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Инвентарный № диска</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Начальник отряда геофизики</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Начальник отряда сейсмических исследований</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Инициатор научной задачи</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Район исследования</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Тип данных</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Прибор</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Степень обработки</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Формат файла</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Объем данных</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>UID</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>UID_рейса</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>выданные каталоги</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Дата выдачи</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ФИО сотрудника</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Подразделение</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Цель выдачи</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Выданный каталог</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Дата возврата</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Возвращено</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Носитель</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>срок моратория/реализации</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Научная задача</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Отметка о реализации</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Дата выполнения</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
@@ -542,14 +592,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14</v>
+        <v>255</v>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ABP56</t>
+          <t>ABP64</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -558,174 +608,234 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>01.12.2025</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>20.12.2025</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Пономаренко Е.П.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>21</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6190001113073</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Ежов В.Е.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>SEB</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Профилограф</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Parasound P70</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>необработанные</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ASD, SEG-Y</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>914 Gb</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>14_ce922dc4__iss_0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>14_ce922dc4</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>09.10.2026</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Чубаренко Б.В.</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Для написания статьи</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>— нет каталогов —</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ASD, SEG-Y, ScreenShot</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>95.9 Gb</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>255_53df8e39__iss_0</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>255_53df8e39</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>ABP64\P70\SEB</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>ЛГА</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Для обработки данных</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>1 год</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>248</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2026</v>
+        <v>2016</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ABP65</t>
+          <t>ANS32</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Академик Борис Петров</t>
+          <t>Академик Николай Страхов</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SEB</t>
+          <t>02.08.2016</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>МЛЭ</t>
+          <t>16.09.2016</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Reson SeaBat T50</t>
+          <t>Пака В.Т.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Обработанные</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>GeoTiff</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>4.99 Gb</t>
-        </is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6190001111735</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>248_dc80d6fe__iss_1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>248_dc80d6fe</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Ежов В.Е.</t>
+          <t>SEB. Борнхольмский, Слупский, Гданьский бассейны</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ЛГА</t>
+          <t>ГЛБО</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Для обработки данных</t>
+          <t>Benthos C3D</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>ABP65\ABP65_UTM34N_GRID</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Hypack project, PrintScreen, журналы</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>7.48 Gb</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1_7e14c3b5__iss_1</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>1_7e14c3b5</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Для написания статьи</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>261</v>
+        <v>26</v>
       </c>
       <c r="B4" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ABP65</t>
+          <t>ABP60</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -734,269 +844,107 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>15.04.2025</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>29.04.2025</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Данченков А.Р.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>19</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6190001113042</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>SEB</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Профилограф</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Parasound P70</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Необработанные</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ASD, SEG-Y</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>80.8 Gb</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>261_c789a9ec__iss_2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>261_c789a9ec</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Ежов В.Е.</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>ЛГА</t>
+          <t>МЛЭ</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>Reson SeaBat T50</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>PDS2000</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2.37 Tb</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>26_c61a8811__iss_2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>26_c61a8811</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Дудков</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>Для обработки данных</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>ABP65\P70</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>247</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ABP65</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Академик Борис Петров</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>65</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SEB</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Профилограф</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Parasound P70</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Необработанные</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ASD, SEG-Y</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>80.8 Gb</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>247_f481fa00__iss_3</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>247_f481fa00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>13.10.2026</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Дудков И</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>ЛГА</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Для обработки данных</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>ABP65\P70</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>13.10.2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>255</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ABP64</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Академик Борис Петров</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>64</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SEB</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Профилограф</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Parasound P70</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Необработанные</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ASD, SEG-Y, ScreenShot</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>95.9 Gb</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>255_53df8e39__iss_4</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>255_53df8e39</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>13.10.2026</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Дудков</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>ЛГА</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Для обработки данных</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>ABP64\P70\SEB</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>проверка проверка</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Данные обработаны</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
